--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20212.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20212.xlsx
@@ -510,25 +510,25 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>94.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -580,22 +580,25 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>68.42</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>31.58</v>
+      </c>
+      <c r="I4" s="2">
+        <v>6.4</v>
       </c>
       <c r="J4">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -612,22 +615,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I5" s="2">
+        <v>6.6</v>
       </c>
       <c r="J5">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -644,25 +650,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>71.88</v>
+        <v>93.75</v>
       </c>
       <c r="H6" s="1">
-        <v>28.13</v>
+        <v>6.25</v>
       </c>
       <c r="I6" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K6" s="1">
-        <v>28.13</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1010,25 +1016,25 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>94.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1080,22 +1086,25 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>68.42</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>31.58</v>
+      </c>
+      <c r="I4" s="2">
+        <v>6.4</v>
       </c>
       <c r="J4">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1112,22 +1121,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I5" s="2">
+        <v>6.6</v>
       </c>
       <c r="J5">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1144,25 +1156,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>71.88</v>
+        <v>93.75</v>
       </c>
       <c r="H6" s="1">
-        <v>28.13</v>
+        <v>6.25</v>
       </c>
       <c r="I6" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K6" s="1">
-        <v>28.13</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="7" spans="1:11">

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20212.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20212.xlsx
@@ -545,25 +545,25 @@
         <v>19</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>89.47</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>10.53</v>
+        <v>5.26</v>
       </c>
       <c r="I3" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>10.53</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -650,25 +650,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>93.75</v>
+        <v>96.88</v>
       </c>
       <c r="H6" s="1">
-        <v>6.25</v>
+        <v>3.13</v>
       </c>
       <c r="I6" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -772,22 +772,25 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -804,22 +807,25 @@
         <v>19</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>5.26</v>
+      </c>
+      <c r="I3" s="2">
+        <v>8.6</v>
       </c>
       <c r="J3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -900,22 +906,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>96.88</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>3.13</v>
+      </c>
+      <c r="I6" s="2">
+        <v>8.9</v>
       </c>
       <c r="J6">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -932,22 +941,25 @@
         <v>19</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>5.26</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8.6</v>
       </c>
       <c r="J7">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>5.26</v>
       </c>
     </row>
   </sheetData>
@@ -1028,7 +1040,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1051,25 +1063,25 @@
         <v>19</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>89.47</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>10.53</v>
+        <v>5.26</v>
       </c>
       <c r="I3" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>10.53</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1156,25 +1168,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>93.75</v>
+        <v>96.88</v>
       </c>
       <c r="H6" s="1">
-        <v>6.25</v>
+        <v>3.13</v>
       </c>
       <c r="I6" s="2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1191,19 +1203,19 @@
         <v>19</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>78.95</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>21.05</v>
+        <v>5.26</v>
       </c>
       <c r="I7" s="2">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="J7">
         <v>0</v>

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20212.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20212.xlsx
@@ -842,22 +842,25 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>57.89</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>42.11</v>
+      </c>
+      <c r="I4" s="2">
+        <v>5.8</v>
       </c>
       <c r="J4">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -874,22 +877,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>50</v>
+      </c>
+      <c r="I5" s="2">
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -906,25 +912,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
         <v>8.9</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1098,19 +1104,19 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G4" s="1">
-        <v>68.42</v>
+        <v>57.89</v>
       </c>
       <c r="H4" s="1">
-        <v>31.58</v>
+        <v>42.11</v>
       </c>
       <c r="I4" s="2">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1133,19 +1139,19 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G5" s="1">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H5" s="1">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I5" s="2">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1168,16 +1174,16 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
         <v>8.800000000000001</v>

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20212.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20212.xlsx
@@ -842,19 +842,19 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>57.89</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>42.11</v>
+        <v>5.26</v>
       </c>
       <c r="I4" s="2">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -877,19 +877,19 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1104,19 +1104,19 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>57.89</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>42.11</v>
+        <v>5.26</v>
       </c>
       <c r="I4" s="2">
-        <v>6.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1139,19 +1139,19 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
         <v>0</v>

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20212.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20212.xlsx
@@ -557,13 +557,13 @@
         <v>5.26</v>
       </c>
       <c r="I3" s="2">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -819,13 +819,13 @@
         <v>5.26</v>
       </c>
       <c r="I3" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1046,7 +1046,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1081,13 +1081,13 @@
         <v>5.26</v>
       </c>
       <c r="I3" s="2">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20212.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20212.xlsx
@@ -959,13 +959,13 @@
         <v>5.26</v>
       </c>
       <c r="I7" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1104,19 +1104,19 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>94.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1151,7 +1151,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1209,19 +1209,19 @@
         <v>19</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>94.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="J7">
         <v>0</v>
